--- a/artfynd/A 49329-2025 artfynd.xlsx
+++ b/artfynd/A 49329-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>96539192</v>
       </c>
       <c r="B21" t="n">
-        <v>89235</v>
+        <v>89237</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49329-2025 artfynd.xlsx
+++ b/artfynd/A 49329-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>96539192</v>
       </c>
       <c r="B21" t="n">
-        <v>89237</v>
+        <v>89239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 49329-2025 artfynd.xlsx
+++ b/artfynd/A 49329-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
         <v>96539192</v>
       </c>
       <c r="B21" t="n">
-        <v>89239</v>
+        <v>89241</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
